--- a/assessment_forms/033_syntactic_knowledge_assessment--assessment_forms.xlsx
+++ b/assessment_forms/033_syntactic_knowledge_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>What is your name</t>
+          <t>Welcome to the Syntactic Knowledge Assessment!</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,36 +548,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Which of the following sentences is grammatically correct</t>
+          <t>Select the grammatically correct sentence</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>answer_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sentence_1</t>
+          <t>Select the correct verb tense</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,41 +589,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Which of the following sentences is grammatically correct</t>
+          <t>Select the correct sentence structure</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>answer_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sentence_2</t>
+          <t>Select the correct agreement</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,18 +635,18 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Which of the following sentences is grammatically correct</t>
+          <t>Select the correct form</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,87 +658,87 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>answer_3</t>
+          <t>question_5_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sentence_3</t>
+          <t>Write a short paragraph about syntax</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>submission</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Which of the following sentences is grammatically correct</t>
+          <t>Submission</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>answer_4</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sentence_4</t>
+          <t>Select the correct punctuation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>submission</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Submission</t>
+          <t>Select the correct clause and phrase structure</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Which of the following sentences is correct in terms of punctuation</t>
+          <t>Select the correct modal and auxiliary verb form</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>answer_5</t>
+          <t>submission_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sentence_5</t>
+          <t>Submission 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -799,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -832,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>this_is_the_correct_sentence.</t>
+          <t>this_is_a_correct_sentence.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>This is the correct sentence.</t>
+          <t>This is a correct sentence.</t>
         </is>
       </c>
     </row>
@@ -849,318 +849,250 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>this_is_a_sentence_that_is_grammatically_incorrect.</t>
+          <t>this_sentence_is_incorrect.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>This is a sentence that is grammatically incorrect.</t>
+          <t>This sentence is incorrect.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>this_is_not_a_grammatically_correct_sentence.</t>
+          <t>this_is_a_correct_sentence_with_correct_verb_tense.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>This is not a grammatically correct sentence.</t>
+          <t>This is a correct sentence with correct verb tense.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_1_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other_(please_specify).</t>
+          <t>this_sentence_has_incorrect_verb_tense.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other (please specify).</t>
+          <t>This sentence has incorrect verb tense.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>this_is_the_correct_sentence.</t>
+          <t>this_is_a_correct_sentence_structure.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>This is the correct sentence.</t>
+          <t>This is a correct sentence structure.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>this_is_a_sentence_that_is_grammatically_incorrect.</t>
+          <t>this_sentence_has_incorrect_structure.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>This is a sentence that is grammatically incorrect.</t>
+          <t>This sentence has incorrect structure.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>this_is_not_a_grammatically_correct_sentence.</t>
+          <t>this_is_a_sentence_with_correct_agreement.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>This is not a grammatically correct sentence.</t>
+          <t>This is a sentence with correct agreement.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_2_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>other_(please_specify).</t>
+          <t>this_sentence_has_incorrect_agreement.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Other (please specify).</t>
+          <t>This sentence has incorrect agreement.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>this_is_the_correct_sentence.</t>
+          <t>this_is_a_correct_sentence_form.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>This is the correct sentence.</t>
+          <t>This is a correct sentence form.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_5_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>this_is_a_sentence_that_is_grammatically_incorrect.</t>
+          <t>this_sentence_has_incorrect_form.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>This is a sentence that is grammatically incorrect.</t>
+          <t>This sentence has incorrect form.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>this_is_not_a_grammatically_correct_sentence.</t>
+          <t>this_is_a_correct_sentence.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>This is not a grammatically correct sentence.</t>
+          <t>This is a correct sentence.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_3_choices</t>
+          <t>question_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>other_(please_specify).</t>
+          <t>this_sentence_is_incorrect.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Other (please specify).</t>
+          <t>This sentence is incorrect.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>this_is_the_correct_sentence.</t>
+          <t>this_is_a_correct_sentence_structure.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>This is the correct sentence.</t>
+          <t>This is a correct sentence structure.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>this_is_a_sentence_that_is_grammatically_incorrect.</t>
+          <t>this_sentence_has_incorrect_structure.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>This is a sentence that is grammatically incorrect.</t>
+          <t>This sentence has incorrect structure.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>this_is_not_a_grammatically_correct_sentence.</t>
+          <t>this_is_a_correct_sentence_form.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>This is not a grammatically correct sentence.</t>
+          <t>This is a correct sentence form.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_4_choices</t>
+          <t>question_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>other_(please_specify).</t>
+          <t>this_sentence_has_incorrect_form.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Other (please specify).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>question_5_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>this_is_the_correct_sentence.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>This is the correct sentence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>question_5_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>this_is_a_sentence_that_is_grammatically_incorrect.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>This is a sentence that is grammatically incorrect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>question_5_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>this_is_not_a_grammatically_correct_sentence.</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>This is not a grammatically correct sentence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>question_5_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>other_(please_specify).</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Other (please specify).</t>
+          <t>This sentence has incorrect form.</t>
         </is>
       </c>
     </row>
